--- a/Feuille_Production_V1.xlsx
+++ b/Feuille_Production_V1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29825"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solidaritetextiles.sharepoint.com/sites/SP_Soltex76/Documents partages/Solidarité/Production/Suivi De Production/Production 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="278" documentId="8_{2F5A9C6E-554B-40AD-A45A-DCE401E07FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF5D8168-939C-496D-BCE5-4B55E16114C9}"/>
+  <xr:revisionPtr revIDLastSave="397" documentId="8_{2F5A9C6E-554B-40AD-A45A-DCE401E07FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF04CDCC-12B1-4368-BFAE-AF70CCD4A440}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{84A198C8-7EAF-4F3C-8F80-08651FB85831}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="23260" windowHeight="12460" xr2:uid="{84A198C8-7EAF-4F3C-8F80-08651FB85831}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,17 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="53">
-  <si>
-    <t>Production    06/03/2026</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="62">
   <si>
     <t>Objectif</t>
   </si>
   <si>
-    <t xml:space="preserve">Entrée atelier : </t>
-  </si>
-  <si>
     <t xml:space="preserve">R3: </t>
   </si>
   <si>
@@ -90,9 +84,6 @@
   </si>
   <si>
     <t>Formation: …</t>
-  </si>
-  <si>
-    <t>Abs: …</t>
   </si>
   <si>
     <t xml:space="preserve">Consigne: </t>
@@ -202,12 +193,6 @@
     <t xml:space="preserve">Commentaire : </t>
   </si>
   <si>
-    <t>Total entrée sur ligne R1 &amp; R2: …</t>
-  </si>
-  <si>
-    <t>Total entrée recyclage R3: …</t>
-  </si>
-  <si>
     <t>Total Général: …</t>
   </si>
   <si>
@@ -215,13 +200,55 @@
   </si>
   <si>
     <t>Direction:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrée Ligne : </t>
+  </si>
+  <si>
+    <t>R4:</t>
+  </si>
+  <si>
+    <t>0,9t</t>
+  </si>
+  <si>
+    <t>Entrée recyclage R4</t>
+  </si>
+  <si>
+    <t>AM: ...</t>
+  </si>
+  <si>
+    <t>Abs injus: …</t>
+  </si>
+  <si>
+    <t>Recyclage R4 (mini 1)</t>
+  </si>
+  <si>
+    <t>Total ligne R1 &amp; R2: …</t>
+  </si>
+  <si>
+    <t>Total  R3: …</t>
+  </si>
+  <si>
+    <t>Total R4: …</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obj: </t>
+  </si>
+  <si>
+    <t>Nok</t>
+  </si>
+  <si>
+    <t>Ok</t>
+  </si>
+  <si>
+    <t>Production    03/04/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,6 +309,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -291,7 +326,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -420,11 +455,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -451,7 +495,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -478,9 +544,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -489,9 +552,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -842,132 +902,132 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AK58"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <dimension ref="A1:AK61"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="37" width="2.7109375" customWidth="1"/>
+    <col min="1" max="37" width="2.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="6.6" customHeight="1">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
-      <c r="S1" s="21"/>
-      <c r="T1" s="21"/>
-      <c r="U1" s="21"/>
-      <c r="V1" s="21"/>
-      <c r="W1" s="21"/>
-      <c r="X1" s="21"/>
-      <c r="Y1" s="21"/>
-      <c r="Z1" s="21"/>
-      <c r="AA1" s="21"/>
-      <c r="AB1" s="21"/>
-      <c r="AC1" s="21"/>
-      <c r="AD1" s="21"/>
-      <c r="AE1" s="21"/>
-      <c r="AF1" s="21"/>
-      <c r="AG1" s="21"/>
-      <c r="AH1" s="21"/>
-      <c r="AI1" s="21"/>
-      <c r="AJ1" s="21"/>
-      <c r="AK1" s="22"/>
-    </row>
-    <row r="2" spans="1:37" ht="14.45" customHeight="1">
-      <c r="A2" s="23"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
-      <c r="Y2" s="24"/>
-      <c r="Z2" s="24"/>
-      <c r="AA2" s="24"/>
-      <c r="AB2" s="24"/>
-      <c r="AC2" s="24"/>
-      <c r="AD2" s="24"/>
-      <c r="AE2" s="24"/>
-      <c r="AF2" s="24"/>
-      <c r="AG2" s="24"/>
-      <c r="AH2" s="24"/>
-      <c r="AI2" s="24"/>
-      <c r="AJ2" s="24"/>
-      <c r="AK2" s="25"/>
-    </row>
-    <row r="3" spans="1:37" ht="8.4499999999999993" customHeight="1" thickBot="1">
-      <c r="A3" s="26"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="27"/>
-      <c r="N3" s="27"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="27"/>
-      <c r="R3" s="27"/>
-      <c r="S3" s="27"/>
-      <c r="T3" s="27"/>
-      <c r="U3" s="27"/>
-      <c r="V3" s="27"/>
-      <c r="W3" s="27"/>
-      <c r="X3" s="27"/>
-      <c r="Y3" s="27"/>
-      <c r="Z3" s="27"/>
-      <c r="AA3" s="27"/>
-      <c r="AB3" s="27"/>
-      <c r="AC3" s="27"/>
-      <c r="AD3" s="27"/>
-      <c r="AE3" s="27"/>
-      <c r="AF3" s="27"/>
-      <c r="AG3" s="27"/>
-      <c r="AH3" s="27"/>
-      <c r="AI3" s="27"/>
-      <c r="AJ3" s="27"/>
-      <c r="AK3" s="28"/>
-    </row>
-    <row r="4" spans="1:37" ht="6.95" customHeight="1" thickBot="1">
+    <row r="1" spans="1:37" ht="6.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
+      <c r="AB1" s="29"/>
+      <c r="AC1" s="29"/>
+      <c r="AD1" s="29"/>
+      <c r="AE1" s="29"/>
+      <c r="AF1" s="29"/>
+      <c r="AG1" s="29"/>
+      <c r="AH1" s="29"/>
+      <c r="AI1" s="29"/>
+      <c r="AJ1" s="29"/>
+      <c r="AK1" s="30"/>
+    </row>
+    <row r="2" spans="1:37" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="31"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="32"/>
+      <c r="X2" s="32"/>
+      <c r="Y2" s="32"/>
+      <c r="Z2" s="32"/>
+      <c r="AA2" s="32"/>
+      <c r="AB2" s="32"/>
+      <c r="AC2" s="32"/>
+      <c r="AD2" s="32"/>
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="32"/>
+      <c r="AG2" s="32"/>
+      <c r="AH2" s="32"/>
+      <c r="AI2" s="32"/>
+      <c r="AJ2" s="32"/>
+      <c r="AK2" s="33"/>
+    </row>
+    <row r="3" spans="1:37" ht="8.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="34"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="35"/>
+      <c r="S3" s="35"/>
+      <c r="T3" s="35"/>
+      <c r="U3" s="35"/>
+      <c r="V3" s="35"/>
+      <c r="W3" s="35"/>
+      <c r="X3" s="35"/>
+      <c r="Y3" s="35"/>
+      <c r="Z3" s="35"/>
+      <c r="AA3" s="35"/>
+      <c r="AB3" s="35"/>
+      <c r="AC3" s="35"/>
+      <c r="AD3" s="35"/>
+      <c r="AE3" s="35"/>
+      <c r="AF3" s="35"/>
+      <c r="AG3" s="35"/>
+      <c r="AH3" s="35"/>
+      <c r="AI3" s="35"/>
+      <c r="AJ3" s="35"/>
+      <c r="AK3" s="36"/>
+    </row>
+    <row r="4" spans="1:37" ht="7" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -998,7 +1058,7 @@
       <c r="AB4" s="8"/>
       <c r="AC4" s="8"/>
     </row>
-    <row r="5" spans="1:37" ht="6.95" customHeight="1">
+    <row r="5" spans="1:37" ht="7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9"/>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -1037,780 +1097,867 @@
       <c r="AJ5" s="1"/>
       <c r="AK5" s="2"/>
     </row>
-    <row r="6" spans="1:37" ht="15.6">
+    <row r="6" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="3"/>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="27"/>
+      <c r="I7" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="AK6" s="3"/>
-    </row>
-    <row r="7" spans="1:37">
-      <c r="A7" s="30" t="s">
+      <c r="J7" s="39"/>
+      <c r="K7" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="L7" s="27"/>
+      <c r="N7" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="O7" s="26"/>
+      <c r="P7" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q7" s="27"/>
+      <c r="AK7" s="3"/>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="33">
-        <v>1.3</v>
-      </c>
-      <c r="G7" s="33"/>
-      <c r="I7" s="32" t="s">
+      <c r="E8" s="40">
+        <v>0.7</v>
+      </c>
+      <c r="F8" s="41"/>
+      <c r="I8" t="s">
         <v>3</v>
       </c>
-      <c r="J7" s="32"/>
-      <c r="K7" s="33">
-        <v>1.3</v>
-      </c>
-      <c r="L7" s="33"/>
-      <c r="O7" t="s">
+      <c r="M8" s="42">
+        <v>0.3</v>
+      </c>
+      <c r="N8" s="43"/>
+      <c r="Q8" t="s">
         <v>4</v>
       </c>
-      <c r="S7" s="34">
-        <v>0.7</v>
-      </c>
-      <c r="T7" s="35"/>
-      <c r="W7" t="s">
+      <c r="S8" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="AA7" s="36">
-        <v>0.3</v>
-      </c>
-      <c r="AB7" s="37"/>
-      <c r="AE7" t="s">
+      <c r="T8" s="41"/>
+      <c r="AA8" s="23"/>
+      <c r="AB8" s="24"/>
+      <c r="AG8" s="22"/>
+      <c r="AH8" s="22"/>
+      <c r="AK8" s="3"/>
+    </row>
+    <row r="9" spans="1:37" ht="7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4"/>
+      <c r="AK9" s="3"/>
+    </row>
+    <row r="10" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="AG7" s="35" t="s">
+      <c r="J10" t="s">
         <v>7</v>
       </c>
-      <c r="AH7" s="35"/>
-      <c r="AK7" s="3"/>
-    </row>
-    <row r="8" spans="1:37" ht="6.95" customHeight="1">
-      <c r="A8" s="4"/>
-      <c r="AK8" s="3"/>
-    </row>
-    <row r="9" spans="1:37" ht="15.6">
-      <c r="A9" s="11" t="s">
+      <c r="L10" s="14"/>
+      <c r="P10" t="s">
         <v>8</v>
       </c>
-      <c r="J9" t="s">
+      <c r="T10" s="14"/>
+      <c r="AK10" s="3"/>
+    </row>
+    <row r="11" spans="1:37" ht="7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="4"/>
+      <c r="AK11" s="3"/>
+    </row>
+    <row r="12" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="L9" s="14"/>
-      <c r="P9" t="s">
+      <c r="J12" t="s">
+        <v>7</v>
+      </c>
+      <c r="L12" s="14"/>
+      <c r="P12" t="s">
+        <v>8</v>
+      </c>
+      <c r="T12" s="14"/>
+      <c r="AK12" s="3"/>
+    </row>
+    <row r="13" spans="1:37" ht="7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="4"/>
+      <c r="AK13" s="3"/>
+    </row>
+    <row r="14" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="T9" s="14"/>
-      <c r="AK9" s="3"/>
-    </row>
-    <row r="10" spans="1:37" ht="6.95" customHeight="1">
-      <c r="A10" s="4"/>
-      <c r="AK10" s="3"/>
-    </row>
-    <row r="11" spans="1:37" ht="15.6">
-      <c r="A11" s="11" t="s">
+      <c r="D14" t="s">
         <v>11</v>
       </c>
-      <c r="J11" t="s">
-        <v>9</v>
-      </c>
-      <c r="L11" s="14"/>
-      <c r="P11" t="s">
-        <v>10</v>
-      </c>
-      <c r="T11" s="14"/>
-      <c r="AK11" s="3"/>
-    </row>
-    <row r="12" spans="1:37" ht="6.95" customHeight="1">
-      <c r="A12" s="4"/>
-      <c r="AK12" s="3"/>
-    </row>
-    <row r="13" spans="1:37" ht="15.6">
-      <c r="A13" s="11" t="s">
+      <c r="G14" t="s">
         <v>12</v>
       </c>
-      <c r="D13" t="s">
+      <c r="K14" t="s">
         <v>13</v>
       </c>
-      <c r="I13" t="s">
+      <c r="S14" t="s">
         <v>14</v>
       </c>
-      <c r="N13" t="s">
+      <c r="W14" t="s">
         <v>15</v>
       </c>
-      <c r="U13" t="s">
+      <c r="AC14" t="s">
+        <v>53</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK14" s="3"/>
+    </row>
+    <row r="15" spans="1:37" ht="7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="11"/>
+      <c r="AK15" s="3"/>
+    </row>
+    <row r="16" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="Z13" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>18</v>
-      </c>
-      <c r="AK13" s="3"/>
-    </row>
-    <row r="14" spans="1:37" ht="6.95" customHeight="1">
-      <c r="A14" s="11"/>
-      <c r="AK14" s="3"/>
-    </row>
-    <row r="15" spans="1:37" ht="15.6">
-      <c r="A15" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
-      <c r="T15" s="31"/>
-      <c r="U15" s="31"/>
-      <c r="AK15" s="3"/>
-    </row>
-    <row r="16" spans="1:37" ht="6.95" customHeight="1">
-      <c r="A16" s="11"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="38"/>
+      <c r="M16" s="38"/>
+      <c r="N16" s="38"/>
+      <c r="O16" s="38"/>
+      <c r="P16" s="38"/>
+      <c r="Q16" s="38"/>
+      <c r="R16" s="38"/>
+      <c r="S16" s="38"/>
+      <c r="T16" s="38"/>
+      <c r="U16" s="38"/>
       <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="1:37" ht="6.95" customHeight="1">
+    <row r="17" spans="1:37" ht="7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="11"/>
       <c r="AK17" s="3"/>
     </row>
-    <row r="18" spans="1:37" ht="6.95" customHeight="1">
-      <c r="A18" s="11"/>
-      <c r="AK18" s="3"/>
-    </row>
-    <row r="19" spans="1:37" ht="6.95" customHeight="1" thickBot="1">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="6"/>
-      <c r="R19" s="6"/>
-      <c r="S19" s="6"/>
-      <c r="T19" s="6"/>
-      <c r="U19" s="6"/>
-      <c r="V19" s="6"/>
-      <c r="W19" s="6"/>
-      <c r="X19" s="6"/>
-      <c r="Y19" s="6"/>
-      <c r="Z19" s="6"/>
-      <c r="AA19" s="6"/>
-      <c r="AB19" s="6"/>
-      <c r="AC19" s="6"/>
-      <c r="AD19" s="6"/>
-      <c r="AE19" s="6"/>
-      <c r="AF19" s="6"/>
-      <c r="AG19" s="6"/>
-      <c r="AH19" s="6"/>
-      <c r="AI19" s="6"/>
-      <c r="AJ19" s="6"/>
-      <c r="AK19" s="7"/>
-    </row>
-    <row r="20" spans="1:37" ht="6.95" customHeight="1" thickBot="1"/>
-    <row r="21" spans="1:37" ht="15.6">
-      <c r="A21" s="12" t="s">
+    <row r="18" spans="1:37" ht="7" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="6"/>
+      <c r="T18" s="6"/>
+      <c r="U18" s="6"/>
+      <c r="V18" s="6"/>
+      <c r="W18" s="6"/>
+      <c r="X18" s="6"/>
+      <c r="Y18" s="6"/>
+      <c r="Z18" s="6"/>
+      <c r="AA18" s="6"/>
+      <c r="AB18" s="6"/>
+      <c r="AC18" s="6"/>
+      <c r="AD18" s="6"/>
+      <c r="AE18" s="6"/>
+      <c r="AF18" s="6"/>
+      <c r="AG18" s="6"/>
+      <c r="AH18" s="6"/>
+      <c r="AI18" s="6"/>
+      <c r="AJ18" s="6"/>
+      <c r="AK18" s="7"/>
+    </row>
+    <row r="19" spans="1:37" ht="7" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="2"/>
+      <c r="S20" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1"/>
+      <c r="W20" s="1"/>
+      <c r="X20" s="1"/>
+      <c r="Y20" s="1"/>
+      <c r="Z20" s="1"/>
+      <c r="AA20" s="1"/>
+      <c r="AB20" s="1"/>
+      <c r="AC20" s="1"/>
+      <c r="AD20" s="1"/>
+      <c r="AE20" s="1"/>
+      <c r="AF20" s="1"/>
+      <c r="AG20" s="1"/>
+      <c r="AH20" s="1"/>
+      <c r="AI20" s="1"/>
+      <c r="AJ20" s="1"/>
+      <c r="AK20" s="2"/>
+    </row>
+    <row r="21" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A21" s="4"/>
+      <c r="H21" t="s">
+        <v>19</v>
+      </c>
+      <c r="M21" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="2"/>
-      <c r="S21" s="12" t="s">
+      <c r="Q21" s="3"/>
+      <c r="S21" s="4"/>
+      <c r="AK21" s="3"/>
+    </row>
+    <row r="22" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
-      <c r="W21" s="1"/>
-      <c r="X21" s="1"/>
-      <c r="Y21" s="1"/>
-      <c r="Z21" s="1"/>
-      <c r="AA21" s="1"/>
-      <c r="AB21" s="1"/>
-      <c r="AC21" s="1"/>
-      <c r="AD21" s="1"/>
-      <c r="AE21" s="1"/>
-      <c r="AF21" s="1"/>
-      <c r="AG21" s="1"/>
-      <c r="AH21" s="1"/>
-      <c r="AI21" s="1"/>
-      <c r="AJ21" s="1"/>
-      <c r="AK21" s="2"/>
-    </row>
-    <row r="22" spans="1:37">
-      <c r="A22" s="4"/>
-      <c r="H22" t="s">
-        <v>22</v>
-      </c>
-      <c r="M22" t="s">
-        <v>23</v>
-      </c>
+      <c r="H22" s="14"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
       <c r="Q22" s="3"/>
       <c r="S22" s="4"/>
       <c r="AK22" s="3"/>
     </row>
-    <row r="23" spans="1:37">
-      <c r="A23" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" s="14"/>
+    <row r="23" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A23" s="4"/>
+      <c r="H23" s="18"/>
       <c r="I23" s="18"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="14"/>
-      <c r="P23" s="14"/>
+      <c r="J23" s="25"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="25"/>
       <c r="Q23" s="3"/>
       <c r="S23" s="4"/>
       <c r="AK23" s="3"/>
     </row>
-    <row r="24" spans="1:37">
-      <c r="A24" s="4"/>
+    <row r="24" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
       <c r="Q24" s="3"/>
       <c r="S24" s="4"/>
       <c r="AK24" s="3"/>
     </row>
-    <row r="25" spans="1:37">
-      <c r="A25" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="14"/>
+    <row r="25" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A25" s="4"/>
       <c r="Q25" s="3"/>
       <c r="S25" s="4"/>
       <c r="AK25" s="3"/>
     </row>
-    <row r="26" spans="1:37">
-      <c r="A26" s="4"/>
+    <row r="26" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="14"/>
       <c r="Q26" s="3"/>
       <c r="S26" s="4"/>
       <c r="AK26" s="3"/>
     </row>
-    <row r="27" spans="1:37">
-      <c r="A27" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="14"/>
-      <c r="O27" s="14"/>
+    <row r="27" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A27" s="4"/>
       <c r="Q27" s="3"/>
       <c r="S27" s="4"/>
       <c r="AK27" s="3"/>
     </row>
-    <row r="28" spans="1:37">
-      <c r="A28" s="4"/>
+    <row r="28" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14"/>
       <c r="Q28" s="3"/>
-      <c r="S28" s="4"/>
+      <c r="S28" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="AK28" s="3"/>
     </row>
-    <row r="29" spans="1:37">
-      <c r="A29" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
-      <c r="O29" s="14"/>
+    <row r="29" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="4"/>
       <c r="Q29" s="3"/>
-      <c r="S29" s="4"/>
+      <c r="S29" s="11"/>
       <c r="AK29" s="3"/>
     </row>
-    <row r="30" spans="1:37">
-      <c r="A30" s="4"/>
+    <row r="30" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
       <c r="Q30" s="3"/>
-      <c r="S30" s="4"/>
+      <c r="S30" s="11"/>
       <c r="AK30" s="3"/>
     </row>
-    <row r="31" spans="1:37">
-      <c r="A31" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
-      <c r="M31" s="14"/>
-      <c r="N31" s="14"/>
-      <c r="O31" s="14"/>
+    <row r="31" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A31" s="4"/>
       <c r="Q31" s="3"/>
       <c r="S31" s="4"/>
       <c r="AK31" s="3"/>
     </row>
-    <row r="32" spans="1:37">
-      <c r="A32" s="4"/>
+    <row r="32" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="14"/>
       <c r="Q32" s="3"/>
       <c r="S32" s="4"/>
       <c r="AK32" s="3"/>
     </row>
-    <row r="33" spans="1:37" ht="15.6">
-      <c r="A33" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
-      <c r="M33" s="14"/>
-      <c r="N33" s="14"/>
-      <c r="O33" s="14"/>
+    <row r="33" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A33" s="4"/>
       <c r="Q33" s="3"/>
-      <c r="S33" s="11" t="s">
-        <v>30</v>
-      </c>
+      <c r="S33" s="4"/>
       <c r="AK33" s="3"/>
     </row>
-    <row r="34" spans="1:37">
-      <c r="A34" s="4"/>
+    <row r="34" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="M34" s="14"/>
+      <c r="N34" s="14"/>
+      <c r="O34" s="14"/>
       <c r="Q34" s="3"/>
-      <c r="S34" s="4"/>
+      <c r="S34" s="11"/>
       <c r="AK34" s="3"/>
     </row>
-    <row r="35" spans="1:37">
-      <c r="A35" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14"/>
-      <c r="M35" s="14"/>
-      <c r="N35" s="14"/>
-      <c r="O35" s="14"/>
+    <row r="35" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A35" s="4"/>
       <c r="Q35" s="3"/>
       <c r="S35" s="4"/>
       <c r="AK35" s="3"/>
     </row>
-    <row r="36" spans="1:37">
-      <c r="A36" s="4"/>
+    <row r="36" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="14"/>
+      <c r="O36" s="14"/>
       <c r="Q36" s="3"/>
-      <c r="S36" s="4"/>
+      <c r="S36" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="AK36" s="3"/>
     </row>
-    <row r="37" spans="1:37">
-      <c r="A37" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
-      <c r="M37" s="14"/>
-      <c r="N37" s="14"/>
-      <c r="O37" s="14"/>
+    <row r="37" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A37" s="4"/>
       <c r="Q37" s="3"/>
       <c r="S37" s="4"/>
       <c r="AK37" s="3"/>
     </row>
-    <row r="38" spans="1:37">
-      <c r="A38" s="4"/>
+    <row r="38" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
+      <c r="M38" s="14"/>
+      <c r="N38" s="14"/>
+      <c r="O38" s="14"/>
       <c r="Q38" s="3"/>
       <c r="S38" s="4"/>
       <c r="AK38" s="3"/>
     </row>
-    <row r="39" spans="1:37">
-      <c r="A39" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
-      <c r="J39" s="14"/>
-      <c r="M39" s="14"/>
-      <c r="N39" s="14"/>
-      <c r="O39" s="14"/>
+    <row r="39" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A39" s="4"/>
       <c r="Q39" s="3"/>
       <c r="S39" s="4"/>
       <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="1:37">
-      <c r="A40" s="4"/>
+    <row r="40" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="14"/>
+      <c r="M40" s="14"/>
+      <c r="N40" s="14"/>
+      <c r="O40" s="14"/>
       <c r="Q40" s="3"/>
       <c r="S40" s="4"/>
       <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="1:37">
-      <c r="A41" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H41" s="14"/>
-      <c r="I41" s="14"/>
-      <c r="J41" s="14"/>
-      <c r="M41" s="14"/>
-      <c r="N41" s="14"/>
-      <c r="O41" s="14"/>
+    <row r="41" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A41" s="4"/>
       <c r="Q41" s="3"/>
       <c r="S41" s="4"/>
       <c r="AK41" s="3"/>
     </row>
-    <row r="42" spans="1:37" ht="6.95" customHeight="1" thickBot="1">
-      <c r="A42" s="5"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="6"/>
-      <c r="L42" s="6"/>
-      <c r="M42" s="6"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="6"/>
-      <c r="Q42" s="7"/>
-      <c r="S42" s="5"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="6"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="6"/>
-      <c r="AB42" s="6"/>
-      <c r="AC42" s="6"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="7"/>
-    </row>
-    <row r="43" spans="1:37" ht="6.95" customHeight="1" thickBot="1"/>
-    <row r="44" spans="1:37" ht="15.6">
-      <c r="A44" s="12" t="s">
+    <row r="42" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="14"/>
+      <c r="M42" s="14"/>
+      <c r="N42" s="14"/>
+      <c r="O42" s="14"/>
+      <c r="Q42" s="3"/>
+      <c r="S42" s="4"/>
+      <c r="AK42" s="3"/>
+    </row>
+    <row r="43" spans="1:37" ht="7" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="5"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="6"/>
+      <c r="O43" s="6"/>
+      <c r="P43" s="6"/>
+      <c r="Q43" s="7"/>
+      <c r="S43" s="5"/>
+      <c r="T43" s="6"/>
+      <c r="U43" s="6"/>
+      <c r="V43" s="6"/>
+      <c r="W43" s="6"/>
+      <c r="X43" s="6"/>
+      <c r="Y43" s="6"/>
+      <c r="Z43" s="6"/>
+      <c r="AA43" s="6"/>
+      <c r="AB43" s="6"/>
+      <c r="AC43" s="6"/>
+      <c r="AD43" s="6"/>
+      <c r="AE43" s="6"/>
+      <c r="AF43" s="6"/>
+      <c r="AG43" s="6"/>
+      <c r="AH43" s="6"/>
+      <c r="AI43" s="6"/>
+      <c r="AJ43" s="6"/>
+      <c r="AK43" s="7"/>
+    </row>
+    <row r="44" spans="1:37" ht="7" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A45" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="2"/>
+      <c r="S45" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1"/>
+      <c r="V45" s="1"/>
+      <c r="W45" s="1"/>
+      <c r="X45" s="1"/>
+      <c r="Y45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z45" s="1"/>
+      <c r="AA45" s="1"/>
+      <c r="AB45" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC45" s="1"/>
+      <c r="AD45" s="1"/>
+      <c r="AE45" s="1"/>
+      <c r="AF45" s="1"/>
+      <c r="AG45" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="1"/>
-      <c r="Q44" s="2"/>
-      <c r="S44" s="12" t="s">
+      <c r="AH45" s="1"/>
+      <c r="AI45" s="1"/>
+      <c r="AJ45" s="1"/>
+      <c r="AK45" s="2"/>
+    </row>
+    <row r="46" spans="1:37" ht="7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="4"/>
+      <c r="Q46" s="3"/>
+      <c r="S46" s="4"/>
+      <c r="AK46" s="3"/>
+    </row>
+    <row r="47" spans="1:37" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="4"/>
+      <c r="B47" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="T44" s="1"/>
-      <c r="U44" s="1"/>
-      <c r="V44" s="1"/>
-      <c r="W44" s="1"/>
-      <c r="X44" s="1"/>
-      <c r="Y44" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z44" s="1"/>
-      <c r="AA44" s="1"/>
-      <c r="AB44" s="1" t="s">
+      <c r="C47" s="39"/>
+      <c r="D47" s="14"/>
+      <c r="F47" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="AC44" s="1"/>
-      <c r="AD44" s="1"/>
-      <c r="AE44" s="1"/>
-      <c r="AF44" s="1"/>
-      <c r="AG44" s="15" t="s">
+      <c r="G47" s="39"/>
+      <c r="H47" s="14"/>
+      <c r="J47" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="AH44" s="1"/>
-      <c r="AI44" s="1"/>
-      <c r="AJ44" s="1"/>
-      <c r="AK44" s="2"/>
-    </row>
-    <row r="45" spans="1:37" ht="6.95" customHeight="1">
-      <c r="A45" s="4"/>
-      <c r="Q45" s="3"/>
-      <c r="S45" s="4"/>
-      <c r="AK45" s="3"/>
-    </row>
-    <row r="46" spans="1:37" ht="14.45" customHeight="1">
-      <c r="A46" s="4"/>
-      <c r="B46" s="32" t="s">
+      <c r="K47" s="39"/>
+      <c r="L47" s="14"/>
+      <c r="N47" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C46" s="32"/>
-      <c r="D46" s="14"/>
-      <c r="F46" s="32" t="s">
+      <c r="O47" s="26"/>
+      <c r="P47" s="14"/>
+      <c r="Q47" s="3"/>
+      <c r="S47" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="G46" s="32"/>
-      <c r="H46" s="14"/>
-      <c r="J46" s="32" t="s">
+      <c r="T47" s="26"/>
+      <c r="U47" s="26"/>
+      <c r="V47" s="14"/>
+      <c r="X47" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="K46" s="32"/>
-      <c r="L46" s="14"/>
-      <c r="N46" s="29" t="s">
+      <c r="Y47" s="38"/>
+      <c r="Z47" s="38"/>
+      <c r="AA47" s="14"/>
+      <c r="AC47" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="O46" s="29"/>
-      <c r="P46" s="14"/>
-      <c r="Q46" s="3"/>
-      <c r="S46" s="30" t="s">
+      <c r="AD47" s="26"/>
+      <c r="AE47" s="26"/>
+      <c r="AF47" s="17"/>
+      <c r="AK47" s="3"/>
+    </row>
+    <row r="48" spans="1:37" ht="7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="5"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
+      <c r="M48" s="6"/>
+      <c r="N48" s="6"/>
+      <c r="O48" s="6"/>
+      <c r="P48" s="6"/>
+      <c r="Q48" s="7"/>
+      <c r="S48" s="5"/>
+      <c r="T48" s="6"/>
+      <c r="U48" s="6"/>
+      <c r="V48" s="6"/>
+      <c r="W48" s="6"/>
+      <c r="X48" s="6"/>
+      <c r="Y48" s="6"/>
+      <c r="Z48" s="6"/>
+      <c r="AA48" s="6"/>
+      <c r="AB48" s="6"/>
+      <c r="AC48" s="6"/>
+      <c r="AD48" s="6"/>
+      <c r="AE48" s="6"/>
+      <c r="AF48" s="6"/>
+      <c r="AG48" s="6"/>
+      <c r="AH48" s="6"/>
+      <c r="AI48" s="6"/>
+      <c r="AJ48" s="6"/>
+      <c r="AK48" s="7"/>
+    </row>
+    <row r="49" spans="1:37" ht="7" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A50" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="T46" s="29"/>
-      <c r="U46" s="29"/>
-      <c r="V46" s="14"/>
-      <c r="X46" s="31" t="s">
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+      <c r="Q50" s="1"/>
+      <c r="R50" s="1"/>
+      <c r="S50" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="Y46" s="31"/>
-      <c r="Z46" s="31"/>
-      <c r="AA46" s="14"/>
-      <c r="AC46" s="29" t="s">
+      <c r="T50" s="1"/>
+      <c r="U50" s="1"/>
+      <c r="V50" s="1"/>
+      <c r="W50" s="1"/>
+      <c r="X50" s="1"/>
+      <c r="Y50" s="1"/>
+      <c r="Z50" s="1"/>
+      <c r="AA50" s="1"/>
+      <c r="AB50" s="1"/>
+      <c r="AC50" s="1"/>
+      <c r="AD50" s="1"/>
+      <c r="AE50" s="1"/>
+      <c r="AF50" s="1"/>
+      <c r="AG50" s="1"/>
+      <c r="AH50" s="1"/>
+      <c r="AI50" s="1"/>
+      <c r="AJ50" s="1"/>
+      <c r="AK50" s="2"/>
+    </row>
+    <row r="51" spans="1:37" ht="7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="4"/>
+      <c r="AK51" s="3"/>
+    </row>
+    <row r="52" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K52" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="M52" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="N52" s="14"/>
+      <c r="P52" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q52" s="14"/>
+      <c r="S52" s="21"/>
+      <c r="AK52" s="3"/>
+    </row>
+    <row r="53" spans="1:37" ht="7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="4"/>
+      <c r="AK53" s="3"/>
+    </row>
+    <row r="54" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="K54" t="s">
+        <v>58</v>
+      </c>
+      <c r="M54" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="N54" s="14"/>
+      <c r="P54" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q54" s="14"/>
+      <c r="AK54" s="3"/>
+    </row>
+    <row r="55" spans="1:37" ht="7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="4"/>
+      <c r="AK55" s="3"/>
+    </row>
+    <row r="56" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="K56" t="s">
+        <v>58</v>
+      </c>
+      <c r="M56" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="N56" s="14"/>
+      <c r="P56" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q56" s="14"/>
+      <c r="AK56" s="3"/>
+    </row>
+    <row r="57" spans="1:37" ht="7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="4"/>
+      <c r="AK57" s="3"/>
+    </row>
+    <row r="58" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="AD46" s="29"/>
-      <c r="AE46" s="29"/>
-      <c r="AF46" s="17"/>
-      <c r="AK46" s="3"/>
-    </row>
-    <row r="47" spans="1:37" ht="6.95" customHeight="1">
-      <c r="A47" s="5"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
-      <c r="L47" s="6"/>
-      <c r="M47" s="6"/>
-      <c r="N47" s="6"/>
-      <c r="O47" s="6"/>
-      <c r="P47" s="6"/>
-      <c r="Q47" s="7"/>
-      <c r="S47" s="5"/>
-      <c r="T47" s="6"/>
-      <c r="U47" s="6"/>
-      <c r="V47" s="6"/>
-      <c r="W47" s="6"/>
-      <c r="X47" s="6"/>
-      <c r="Y47" s="6"/>
-      <c r="Z47" s="6"/>
-      <c r="AA47" s="6"/>
-      <c r="AB47" s="6"/>
-      <c r="AC47" s="6"/>
-      <c r="AD47" s="6"/>
-      <c r="AE47" s="6"/>
-      <c r="AF47" s="6"/>
-      <c r="AG47" s="6"/>
-      <c r="AH47" s="6"/>
-      <c r="AI47" s="6"/>
-      <c r="AJ47" s="6"/>
-      <c r="AK47" s="7"/>
-    </row>
-    <row r="48" spans="1:37" ht="6.95" customHeight="1" thickBot="1"/>
-    <row r="49" spans="1:37" ht="15.6">
-      <c r="A49" s="12" t="s">
+      <c r="K58" t="s">
+        <v>58</v>
+      </c>
+      <c r="M58" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="N58" s="14"/>
+      <c r="P58" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q58" s="14"/>
+      <c r="AK58" s="3"/>
+    </row>
+    <row r="59" spans="1:37" ht="7" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="5"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6"/>
+      <c r="M59" s="6"/>
+      <c r="N59" s="6"/>
+      <c r="O59" s="6"/>
+      <c r="P59" s="6"/>
+      <c r="Q59" s="6"/>
+      <c r="R59" s="6"/>
+      <c r="S59" s="6"/>
+      <c r="T59" s="6"/>
+      <c r="U59" s="6"/>
+      <c r="V59" s="6"/>
+      <c r="W59" s="6"/>
+      <c r="X59" s="6"/>
+      <c r="Y59" s="6"/>
+      <c r="Z59" s="6"/>
+      <c r="AA59" s="6"/>
+      <c r="AB59" s="6"/>
+      <c r="AC59" s="6"/>
+      <c r="AD59" s="6"/>
+      <c r="AE59" s="6"/>
+      <c r="AF59" s="6"/>
+      <c r="AG59" s="6"/>
+      <c r="AH59" s="6"/>
+      <c r="AI59" s="6"/>
+      <c r="AJ59" s="6"/>
+      <c r="AK59" s="7"/>
+    </row>
+    <row r="61" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A61" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
-      <c r="N49" s="16" t="s">
+      <c r="G61" t="s">
+        <v>7</v>
+      </c>
+      <c r="I61" s="14"/>
+      <c r="M61" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q61" s="14"/>
+      <c r="Z61" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="O49" s="1"/>
-      <c r="P49" s="1"/>
-      <c r="Q49" s="1"/>
-      <c r="R49" s="1"/>
-      <c r="S49" s="1"/>
-      <c r="T49" s="1"/>
-      <c r="U49" s="1"/>
-      <c r="V49" s="1"/>
-      <c r="W49" s="1"/>
-      <c r="X49" s="1"/>
-      <c r="Y49" s="1"/>
-      <c r="Z49" s="1"/>
-      <c r="AA49" s="1"/>
-      <c r="AB49" s="1"/>
-      <c r="AC49" s="1"/>
-      <c r="AD49" s="1"/>
-      <c r="AE49" s="1"/>
-      <c r="AF49" s="1"/>
-      <c r="AG49" s="1"/>
-      <c r="AH49" s="1"/>
-      <c r="AI49" s="1"/>
-      <c r="AJ49" s="1"/>
-      <c r="AK49" s="2"/>
-    </row>
-    <row r="50" spans="1:37" ht="6.95" customHeight="1">
-      <c r="A50" s="4"/>
-      <c r="AK50" s="3"/>
-    </row>
-    <row r="51" spans="1:37">
-      <c r="A51" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK51" s="3"/>
-    </row>
-    <row r="52" spans="1:37" ht="6.95" customHeight="1">
-      <c r="A52" s="4"/>
-      <c r="AK52" s="3"/>
-    </row>
-    <row r="53" spans="1:37">
-      <c r="A53" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AK53" s="3"/>
-    </row>
-    <row r="54" spans="1:37" ht="6.95" customHeight="1">
-      <c r="A54" s="4"/>
-      <c r="AK54" s="3"/>
-    </row>
-    <row r="55" spans="1:37">
-      <c r="A55" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AK55" s="3"/>
-    </row>
-    <row r="56" spans="1:37" ht="6.95" customHeight="1" thickBot="1">
-      <c r="A56" s="5"/>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
-      <c r="K56" s="6"/>
-      <c r="L56" s="6"/>
-      <c r="M56" s="6"/>
-      <c r="N56" s="6"/>
-      <c r="O56" s="6"/>
-      <c r="P56" s="6"/>
-      <c r="Q56" s="6"/>
-      <c r="R56" s="6"/>
-      <c r="S56" s="6"/>
-      <c r="T56" s="6"/>
-      <c r="U56" s="6"/>
-      <c r="V56" s="6"/>
-      <c r="W56" s="6"/>
-      <c r="X56" s="6"/>
-      <c r="Y56" s="6"/>
-      <c r="Z56" s="6"/>
-      <c r="AA56" s="6"/>
-      <c r="AB56" s="6"/>
-      <c r="AC56" s="6"/>
-      <c r="AD56" s="6"/>
-      <c r="AE56" s="6"/>
-      <c r="AF56" s="6"/>
-      <c r="AG56" s="6"/>
-      <c r="AH56" s="6"/>
-      <c r="AI56" s="6"/>
-      <c r="AJ56" s="6"/>
-      <c r="AK56" s="7"/>
-    </row>
-    <row r="58" spans="1:37">
-      <c r="A58" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="G58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I58" s="14"/>
-      <c r="M58" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q58" s="14"/>
-      <c r="Z58" s="19" t="s">
-        <v>52</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
+    <mergeCell ref="E16:U16"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="P7:Q7"/>
     <mergeCell ref="A1:AK3"/>
-    <mergeCell ref="N46:O46"/>
-    <mergeCell ref="S46:U46"/>
-    <mergeCell ref="X46:Z46"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="AC46:AE46"/>
+    <mergeCell ref="N47:O47"/>
+    <mergeCell ref="S47:U47"/>
+    <mergeCell ref="X47:Z47"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="J47:K47"/>
+    <mergeCell ref="AC47:AE47"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="K7:L7"/>
     <mergeCell ref="I7:J7"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="AA7:AB7"/>
-    <mergeCell ref="AG7:AH7"/>
-    <mergeCell ref="E15:U15"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="S8:T8"/>
   </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010045D25A3C2B1B5D4089B44CA276A34A36" ma:contentTypeVersion="11" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="7a3f86ba7c7f71137e2b7d265313e9eb">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bfb3f432-878f-40b7-a9c6-5eebb15c279a" xmlns:ns3="43d6646e-9d5d-4e3d-a78b-40907916a221" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1a2662133611dafe6e6116d18f627594" ns2:_="" ns3:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010045D25A3C2B1B5D4089B44CA276A34A36" ma:contentTypeVersion="12" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="4c893e36bfdd1f18b56837fc233c4f44">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bfb3f432-878f-40b7-a9c6-5eebb15c279a" xmlns:ns3="43d6646e-9d5d-4e3d-a78b-40907916a221" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cc20b2a12f56ed53bbaaf4e2506fd255" ns2:_="" ns3:_="">
     <xsd:import namespace="bfb3f432-878f-40b7-a9c6-5eebb15c279a"/>
     <xsd:import namespace="43d6646e-9d5d-4e3d-a78b-40907916a221"/>
     <xsd:element name="properties">
@@ -1829,6 +1976,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -1886,6 +2034,11 @@
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -2003,15 +2156,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2024,13 +2168,45 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D74932EC-34C9-4274-9FE4-FB3959D34DE6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4925CBBA-87CC-492A-9066-6F2C361FEADE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4925CBBA-87CC-492A-9066-6F2C361FEADE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{697AB9B1-00B7-4CDA-AFD3-CB82F8D9ABFC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="bfb3f432-878f-40b7-a9c6-5eebb15c279a"/>
+    <ds:schemaRef ds:uri="43d6646e-9d5d-4e3d-a78b-40907916a221"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5C166E5-0B1D-4283-984C-925460CE4722}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5C166E5-0B1D-4283-984C-925460CE4722}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="43d6646e-9d5d-4e3d-a78b-40907916a221"/>
+    <ds:schemaRef ds:uri="bfb3f432-878f-40b7-a9c6-5eebb15c279a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>